--- a/CPF-IA-Cockpit-TEMPLATE.xlsx
+++ b/CPF-IA-Cockpit-TEMPLATE.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="M1" s="3" t="inlineStr">
         <is>
-          <t>← REMPLIS LA COLONNE EMAIL (B) : c'est la clé de connexion de chaque apprenant</t>
+          <t>← Christelle : ajoute son email quand tu l'as</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,11 @@
           <t>Barbara</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>barbara_ch@yahoo.fr</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>S1</t>
@@ -585,7 +589,11 @@
           <t>Adouayi</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>adouayi@gmail.com</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>S1</t>
@@ -636,7 +644,11 @@
           <t>Cyril</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>cyril.blanchard28@gmail.com</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>S1</t>
@@ -687,7 +699,11 @@
           <t>Maël</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>maelprudhomme689@gmail.com</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>S1</t>
